--- a/argus/kship/models/013030_model.xlsx
+++ b/argus/kship/models/013030_model.xlsx
@@ -4145,7 +4145,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-09-30</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -4273,7 +4273,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 7.8, "op_wape_pct": 0.8, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 473.52, "rev_act": 538.45, "op_pred": 142.99, "op_act": 141.98}, {"q": "2025Q4", "rev_pred": 516.21, "rev_act": 573.52, "op_pred": 155.87, "op_act": 155.81}, {"q": "2026Q1", "rev_pred": 512.74, "rev_act": 541.46, "op_pred": 154.83, "op_act": 156.86}, {"q": "2026Q2", "rev_pred": 568.14, "rev_act": 592.51, "op_pred": 171.56, "op_act": 169.91}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 7.8, "op_wape_pct": 0.8, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "selection_oos_at_freeze": null, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 473.52, "rev_act": 538.45, "op_pred": 142.99, "op_act": 141.98}, {"q": "2025Q4", "rev_pred": 516.21, "rev_act": 573.52, "op_pred": 155.87, "op_act": 155.81}, {"q": "2026Q1", "rev_pred": 512.74, "rev_act": 541.46, "op_pred": 154.83, "op_act": 156.86}, {"q": "2026Q2", "rev_pred": 568.14, "rev_act": 592.51, "op_pred": 171.56, "op_act": 169.91}]}</t>
         </is>
       </c>
     </row>
@@ -9738,7 +9738,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -16196,7 +16196,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/013030_model.xlsx
+++ b/argus/kship/models/013030_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -3604,7 +3604,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -4475,35 +4475,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4594,35 +4594,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4713,35 +4713,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -4832,35 +4832,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -4951,35 +4951,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5070,35 +5070,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5189,35 +5189,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5308,35 +5308,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5443,7 +5443,7 @@
         <v>36650</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>36350</v>
+        <v>35650</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5625,7 +5625,7 @@
         <v>27550</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>35900</v>
+        <v>35600</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -5716,7 +5716,7 @@
         <v>32882.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>36525</v>
+        <v>36233.3</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="D38" s="34" t="n">
-        <v>36350</v>
+        <v>35650</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
@@ -7917,7 +7917,7 @@
       </c>
       <c r="D39" s="35" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -8230,7 +8230,7 @@
         </is>
       </c>
       <c r="D47" s="36" t="n">
-        <v>0.9910103676991435</v>
+        <v>0.9910103676991434</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -8743,7 +8743,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -15201,7 +15201,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -27069,7 +27069,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31562,7 +31562,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33482,7 +33482,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>7.32</v>
+        <v>7.18</v>
       </c>
     </row>
     <row r="32">
@@ -33492,7 +33492,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.91</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/013030_model.xlsx
+++ b/argus/kship/models/013030_model.xlsx
@@ -3604,7 +3604,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -4475,35 +4475,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4594,35 +4594,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4713,35 +4713,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -4832,35 +4832,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -4951,35 +4951,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5070,35 +5070,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5189,35 +5189,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5308,35 +5308,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5443,7 +5443,7 @@
         <v>36650</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>35650</v>
+        <v>34900</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5625,7 +5625,7 @@
         <v>27550</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>35600</v>
+        <v>34750</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -5716,7 +5716,7 @@
         <v>32882.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>36233.3</v>
+        <v>35912.5</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -7877,11 +7877,11 @@
         </is>
       </c>
       <c r="D38" s="34" t="n">
-        <v>35650</v>
+        <v>34900</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 36,350원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 36,300원)</t>
         </is>
       </c>
       <c r="F38" s="9" t="n"/>
@@ -7917,7 +7917,7 @@
       </c>
       <c r="D39" s="35" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -8743,7 +8743,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -15201,7 +15201,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -27069,7 +27069,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31562,7 +31562,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33482,7 +33482,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>7.18</v>
+        <v>7.03</v>
       </c>
     </row>
     <row r="32">
@@ -33492,7 +33492,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/013030_model.xlsx
+++ b/argus/kship/models/013030_model.xlsx
@@ -3604,7 +3604,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -8743,7 +8743,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -15201,7 +15201,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/013030_model.xlsx
+++ b/argus/kship/models/013030_model.xlsx
@@ -4475,35 +4475,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4594,35 +4594,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4713,35 +4713,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -4832,35 +4832,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -4951,35 +4951,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5070,35 +5070,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5189,35 +5189,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5308,35 +5308,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5443,7 +5443,7 @@
         <v>36650</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>34900</v>
+        <v>34300</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5625,7 +5625,7 @@
         <v>27550</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>34750</v>
+        <v>34250</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -5716,7 +5716,7 @@
         <v>32882.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>35912.5</v>
+        <v>35570</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -7877,11 +7877,11 @@
         </is>
       </c>
       <c r="D38" s="34" t="n">
-        <v>34900</v>
+        <v>34300</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 36,300원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 35,650원)</t>
         </is>
       </c>
       <c r="F38" s="9" t="n"/>
@@ -7917,7 +7917,7 @@
       </c>
       <c r="D39" s="35" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -27069,7 +27069,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31562,7 +31562,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33482,7 +33482,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>7.03</v>
+        <v>6.91</v>
       </c>
     </row>
     <row r="32">
@@ -33492,7 +33492,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/013030_model.xlsx
+++ b/argus/kship/models/013030_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -3604,7 +3604,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -8230,7 +8230,7 @@
         </is>
       </c>
       <c r="D47" s="36" t="n">
-        <v>0.9910103676991434</v>
+        <v>0.9910103676991435</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -8743,7 +8743,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -15201,7 +15201,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/013030_model.xlsx
+++ b/argus/kship/models/013030_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -4475,35 +4475,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4594,35 +4594,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4713,35 +4713,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -4832,35 +4832,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -4951,35 +4951,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5070,35 +5070,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5189,35 +5189,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5308,35 +5308,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5443,7 +5443,7 @@
         <v>36650</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>34300</v>
+        <v>34400</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5625,7 +5625,7 @@
         <v>27550</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>34250</v>
+        <v>34200</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -5716,7 +5716,7 @@
         <v>32882.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>35570</v>
+        <v>35590</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -7877,11 +7877,11 @@
         </is>
       </c>
       <c r="D38" s="34" t="n">
-        <v>34300</v>
+        <v>34400</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 35,650원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 34,800원)</t>
         </is>
       </c>
       <c r="F38" s="9" t="n"/>
@@ -8230,7 +8230,7 @@
         </is>
       </c>
       <c r="D47" s="36" t="n">
-        <v>0.9910103676991435</v>
+        <v>0.9910103676991434</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -33482,7 +33482,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6.91</v>
+        <v>6.93</v>
       </c>
     </row>
     <row r="32">

--- a/argus/kship/models/013030_model.xlsx
+++ b/argus/kship/models/013030_model.xlsx
@@ -3604,7 +3604,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -4475,35 +4475,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4594,35 +4594,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4713,35 +4713,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -4832,35 +4832,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -4951,35 +4951,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5070,35 +5070,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5189,35 +5189,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5308,35 +5308,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -8743,7 +8743,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -15201,7 +15201,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/013030_model.xlsx
+++ b/argus/kship/models/013030_model.xlsx
@@ -3604,7 +3604,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -8743,7 +8743,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -15201,7 +15201,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/013030_model.xlsx
+++ b/argus/kship/models/013030_model.xlsx
@@ -3604,7 +3604,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -5443,7 +5443,7 @@
         <v>36650</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>34400</v>
+        <v>33350</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5625,7 +5625,7 @@
         <v>27550</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>34200</v>
+        <v>33000</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -5716,7 +5716,7 @@
         <v>32882.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>35590</v>
+        <v>35216.7</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="D38" s="34" t="n">
-        <v>34400</v>
+        <v>33350</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
@@ -7917,7 +7917,7 @@
       </c>
       <c r="D39" s="35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -8743,7 +8743,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -15201,7 +15201,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -27069,7 +27069,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31562,7 +31562,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33482,7 +33482,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6.93</v>
+        <v>6.72</v>
       </c>
     </row>
     <row r="32">
@@ -33492,7 +33492,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/013030_model.xlsx
+++ b/argus/kship/models/013030_model.xlsx
@@ -3604,7 +3604,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -4475,35 +4475,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4594,35 +4594,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4713,35 +4713,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -4832,35 +4832,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -4951,35 +4951,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5070,35 +5070,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5189,35 +5189,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5308,35 +5308,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5443,7 +5443,7 @@
         <v>36650</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>33350</v>
+        <v>32800</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5625,7 +5625,7 @@
         <v>27550</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>33000</v>
+        <v>31700</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -5716,7 +5716,7 @@
         <v>32882.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>35216.7</v>
+        <v>34871.4</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -7877,11 +7877,11 @@
         </is>
       </c>
       <c r="D38" s="34" t="n">
-        <v>33350</v>
+        <v>32800</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 34,800원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 34,450원)</t>
         </is>
       </c>
       <c r="F38" s="9" t="n"/>
@@ -7917,7 +7917,7 @@
       </c>
       <c r="D39" s="35" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -8743,7 +8743,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -15201,7 +15201,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -27069,7 +27069,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31562,7 +31562,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33482,7 +33482,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6.72</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="32">
@@ -33492,7 +33492,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/013030_model.xlsx
+++ b/argus/kship/models/013030_model.xlsx
@@ -3604,7 +3604,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4475,35 +4475,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4594,35 +4594,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4713,35 +4713,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -4832,35 +4832,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -4951,35 +4951,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5070,35 +5070,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5189,35 +5189,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5308,35 +5308,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5443,7 +5443,7 @@
         <v>36650</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>32800</v>
+        <v>33000</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5716,7 +5716,7 @@
         <v>32882.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>34871.4</v>
+        <v>34662.5</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -7877,11 +7877,11 @@
         </is>
       </c>
       <c r="D38" s="34" t="n">
-        <v>32800</v>
+        <v>33000</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 34,450원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 33,250원)</t>
         </is>
       </c>
       <c r="F38" s="9" t="n"/>
@@ -7917,7 +7917,7 @@
       </c>
       <c r="D39" s="35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -8743,7 +8743,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -15201,7 +15201,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -27069,7 +27069,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31562,7 +31562,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33482,7 +33482,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6.61</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="32">

--- a/argus/kship/models/013030_model.xlsx
+++ b/argus/kship/models/013030_model.xlsx
@@ -3604,7 +3604,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -4475,35 +4475,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4594,35 +4594,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4713,35 +4713,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -4832,35 +4832,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -4951,35 +4951,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5070,35 +5070,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5189,35 +5189,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5308,35 +5308,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5443,7 +5443,7 @@
         <v>36650</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>33000</v>
+        <v>32000</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5625,7 +5625,7 @@
         <v>27550</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>31700</v>
+        <v>31250</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -5716,7 +5716,7 @@
         <v>32882.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>34662.5</v>
+        <v>34009.1</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -7877,11 +7877,11 @@
         </is>
       </c>
       <c r="D38" s="34" t="n">
-        <v>33000</v>
+        <v>32000</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 33,250원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 31,700원)</t>
         </is>
       </c>
       <c r="F38" s="9" t="n"/>
@@ -7917,7 +7917,7 @@
       </c>
       <c r="D39" s="35" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -8743,7 +8743,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -15201,7 +15201,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -27069,7 +27069,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31562,7 +31562,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33482,7 +33482,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6.65</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="32">
@@ -33492,7 +33492,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/013030_model.xlsx
+++ b/argus/kship/models/013030_model.xlsx
@@ -3604,7 +3604,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4475,35 +4475,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4594,35 +4594,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4713,35 +4713,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -4832,35 +4832,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -4951,35 +4951,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5070,35 +5070,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5189,35 +5189,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5308,35 +5308,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5443,7 +5443,7 @@
         <v>36650</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>32000</v>
+        <v>30000</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5625,7 +5625,7 @@
         <v>27550</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>31250</v>
+        <v>29850</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -5716,7 +5716,7 @@
         <v>32882.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>34009.1</v>
+        <v>33096.9</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -7877,11 +7877,11 @@
         </is>
       </c>
       <c r="D38" s="34" t="n">
-        <v>32000</v>
+        <v>30000</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 31,700원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 31,000원)</t>
         </is>
       </c>
       <c r="F38" s="9" t="n"/>
@@ -7917,7 +7917,7 @@
       </c>
       <c r="D39" s="35" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -8743,7 +8743,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -15201,7 +15201,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -27069,7 +27069,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31562,7 +31562,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33482,7 +33482,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6.44</v>
+        <v>6.04</v>
       </c>
     </row>
     <row r="32">
@@ -33492,7 +33492,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="33">
